--- a/docs/LOAD_RATIO_REVIEW_2026-07-28.xlsx
+++ b/docs/LOAD_RATIO_REVIEW_2026-07-28.xlsx
@@ -52,7 +52,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E0F0E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -62,7 +62,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0F0E0"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="84" customWidth="1" min="1" max="1"/>
@@ -484,7 +484,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">  1 Anchor multipliers   13 rows   UPSTREAM OF EVERYTHING. Rule first.</t>
+          <t xml:space="preserve">  1 Anchor multipliers   13 rows   RULED 2026-07-28 — done, shown for reference.</t>
         </is>
       </c>
     </row>
@@ -498,21 +498,21 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">  3 Plausible ratios     61 rows   a skim.</t>
+          <t xml:space="preserve">  3 Plausible ratios     63 rows   a skim.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">  4 Floor-out ratios      6 rows   these currently do NOTHING.</t>
+          <t xml:space="preserve">  4 Floor-out ratios      4 rows   these currently do NOTHING.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  5 Already ruled         6 rows   context only, no action.</t>
+          <t xml:space="preserve">  5 Already ruled         6 rows   ruled 2026-07-25, context only.</t>
         </is>
       </c>
     </row>
@@ -536,118 +536,118 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>WHY THE MULTIPLIERS COME FIRST</t>
+          <t>WHAT YOUR MULTIPLIER RULINGS CHANGED IN THIS SHEET</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Anchor 1RM = bodyweight x multiplier. All 77 ratios then multiply that anchor.</t>
+          <t>The bench ladder moved 0.65 -&gt; 0.75, so the reference bench anchor rose from</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>An error on tab 1 moves every suggested weight in the app at once, so ruling</t>
+          <t>57.2 kg to 66 kg and EVERY bench-anchored kg below was recomputed. Two ratios</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>the ratios first would mean ruling them against a baseline not yet agreed.</t>
+          <t>stopped flooring out as a result (Concentration Curl, Dumbbell Kickback), so</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>floor-out is 4 rows, not the 6 flagged before your ruling. Nothing was</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>HOW A RATIO WORKS</t>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>reclassified by hand — the flags are recomputed from the ruled anchors.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  working weight = anchor 1RM x ratio, rounded to the equipment increment,</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t xml:space="preserve">                   then floored at the equipment minimum.</t>
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>WHY THE MULTIPLIERS CAME FIRST</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>The ratio is NOT a percentage of 1RM. It bakes in the rep-range discount, so</t>
+          <t>Anchor 1RM = bodyweight x multiplier. All 77 ratios then multiply that anchor.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>the output is a direct working weight.</t>
+          <t>An error on tab 1 moves every suggested weight in the app at once, so ruling</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>the ratios first would have meant ruling them against a baseline not yet</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>THE "kg @ ref athlete" COLUMN ON TABS 2-5</t>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>agreed. That is why your ladder rulings changed two flags here.</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Computed at squat 1RM = 88 kg. That is a REVIEW-TIME reference athlete, chosen</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>so the sheet could be checked against your 2026-07-25 ruling figures. It is</t>
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>HOW A RATIO WORKS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NOT a runtime constant — no athlete is pinned at 88 kg. Every athlete gets</t>
+          <t xml:space="preserve">  working weight = anchor 1RM x ratio, rounded to the equipment increment,</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>their own anchor from their own bodyweight and strength answer (tab 1).</t>
+          <t xml:space="preserve">                   then floored at the equipment minimum.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Read it as "what this ratio produces for one athlete", not "what everyone</t>
+          <t>The ratio is NOT a percentage of 1RM. It bakes in the rep-range discount, so</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>gets". The RATIO is the thing being ruled.</t>
+          <t>the output is a direct working weight.</t>
         </is>
       </c>
     </row>
@@ -655,135 +655,149 @@
       <c r="A31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>bench 1RM = 57.2 kg (0.65 x 88) is an ASSUMPTION — your 2026-07-25 ruling</t>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>A KNOWN STOPGAP — the baked-in rep assumption</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>pinned squat and never pinned bench. Tab 1 is where that gets fixed.</t>
+          <t>Because the ratio bakes in a rep-range discount, it silently assumes ONE rep</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>scheme. When the Sam-authored rep-max continuum lands (Master Plan 4.1a),</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>THE MISSING-BODYWEIGHT FALLBACK (last row of tab 1)</t>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>starting estimates become rep-aware: anchor -&gt; implied max -&gt; % for the</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>If an athlete has no bodyweight recorded the code substitutes 82 kg ("average</t>
+          <t>prescribed reps. At that point most per-exercise ratios are candidates to</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AFL player"). Nobody authored that. Two ways to settle it:</t>
+          <t>collapse into simpler relative-strength ratios plus that one table.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">  A. Give a number you will stand behind — it stays a default.</t>
+          <t>So these rulings are FIRST-SESSION VALUES, not permanent law.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  B. FAIL LOUD: refuse to print a weight when bodyweight is unknown, the way</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">     an unauthored exercise now shows "-" rather than a confident "BW".</t>
+          <t>THE "kg @ ref athlete" COLUMN ON TABS 2-5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">     Costs a number on the card for an athlete who skipped the question;</t>
+          <t>Computed at squat 1RM = 88 kg (your 2026-07-25 reference athlete) and bench</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">     buys never guessing an athlete's bodyweight to two figures.</t>
+          <t>1RM = 66 kg (88 x your ruled 0.75). It is a REVIEW-TIME reference athlete, NOT</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Write a number, or the word FAIL LOUD, in that row's "SAM: value" cell.</t>
+          <t>a runtime constant — no athlete is pinned there. Every athlete gets their own</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>anchor from their own bodyweight and strength answer (tab 1). Read it as</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>WHAT MY FLAGS MEAN</t>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>"what this ratio produces for one athlete". The RATIO is what is being ruled.</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>A starting point, not a verdict. "plausible" means nothing looked wrong to me.</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>WHAT MY FLAGS MEAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A starting point, not a verdict. "plausible" means nothing looked wrong to me.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>I am not an S&amp;C coach; it is not evidence the number is right.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>AFTER SIGN-OFF</t>
-        </is>
-      </c>
-    </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>This workbook becomes the source of truth and the code follows it, held by an</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>equality test in both directions — same arrangement as the conditioning</t>
+          <t>AFTER SIGN-OFF</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
+        <is>
+          <t>This workbook becomes the source of truth and the code follows it, held by an</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>equality test in both directions — same arrangement as the conditioning</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
         <is>
           <t>templates. A hand-edited ratio then fails the build.</t>
         </is>
@@ -831,7 +845,7 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
-          <t>Current value</t>
+          <t>RULED value</t>
         </is>
       </c>
       <c r="E1" s="3" t="inlineStr">
@@ -846,350 +860,406 @@
       </c>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>SAM: value</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="H1" s="3" t="inlineStr">
         <is>
-          <t>SAM: notes</t>
+          <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>squat multiplier</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>I don't squat</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>squat</t>
         </is>
       </c>
-      <c r="D2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E2" t="n">
-        <v>48</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="D2" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" s="4" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>squat multiplier</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>Less than bodyweight</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>squat</t>
         </is>
       </c>
-      <c r="D3" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E3" t="n">
-        <v>64</v>
-      </c>
-      <c r="F3" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="D3" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>squat multiplier</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>Around bodyweight</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>squat</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="D4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>squat multiplier</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>1.5x bodyweight</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>squat</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D5" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5" s="4" t="n">
         <v>97.5</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>squat multiplier</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>2x bodyweight+</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>squat</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6" s="4" t="n">
         <v>130</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>squat multiplier</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Not sure</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>squat</t>
         </is>
       </c>
-      <c r="D7" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E7" t="n">
-        <v>64</v>
-      </c>
-      <c r="F7" t="n">
-        <v>52.5</v>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="D7" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>TIED to "Less than bodyweight" — if that changes, this follows</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>bench multiplier</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>I don't bench</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E8" t="n">
-        <v>32</v>
-      </c>
-      <c r="F8" t="n">
-        <v>25</v>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>bench multiplier</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Less than bodyweight</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E9" t="n">
-        <v>52</v>
-      </c>
-      <c r="F9" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>bench multiplier</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Around bodyweight</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="4" t="n">
         <v>65</v>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>bench multiplier</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>1.25x bodyweight</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="E11" t="n">
+      <c r="E11" s="4" t="n">
         <v>100</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11" s="4" t="n">
         <v>82.5</v>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>bench multiplier</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>1.5x bodyweight+</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="n">
         <v>1.5</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12" s="4" t="n">
         <v>97.5</v>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>bench multiplier</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Not sure</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E13" t="n">
-        <v>52</v>
-      </c>
-      <c r="F13" t="n">
-        <v>42.5</v>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>60</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>TIED to "Less than bodyweight" — if that changes, this follows</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1207,23 +1277,29 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
-        <v>82</v>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>FAIL LOUD</t>
+        </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>none</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr"/>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>RULED 2026-07-28</t>
+        </is>
+      </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>a number, or FAIL LOUD — see Architecture &amp; Rules</t>
+          <t>no default — no bodyweight means no anchor and no prescribed weight</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1419,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
@@ -1403,7 +1479,7 @@
         </is>
       </c>
       <c r="E5" s="5" t="n">
-        <v>20</v>
+        <v>22.5</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1424,7 +1500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:H64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1529,7 +1605,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1589,7 +1665,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>47.5</v>
+        <v>55</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1619,7 +1695,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1799,7 +1875,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1829,7 +1905,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1859,7 +1935,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1889,7 +1965,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>42.5</v>
+        <v>50</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1902,7 +1978,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DB Bench Press</t>
+          <t>Concentration Curl</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1911,7 +1987,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.32</v>
+        <v>0.08</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1919,7 +1995,7 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>17.5</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1932,7 +2008,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DB Shoulder Press</t>
+          <t>DB Bench Press</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1941,7 +2017,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1949,7 +2025,7 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.5</v>
+        <v>20</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1962,7 +2038,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Dumbbell Skull Crusher</t>
+          <t>DB Shoulder Press</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1971,7 +2047,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.14</v>
+        <v>0.22</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1979,7 +2055,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>7.5</v>
+        <v>15</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1992,7 +2068,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Face Pull</t>
+          <t>Dumbbell Kickback</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2001,15 +2077,15 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.18</v>
+        <v>0.08</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>dumbbell</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2022,24 +2098,24 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Front Squat</t>
+          <t>Dumbbell Skull Crusher</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.7</v>
+        <v>0.14</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>dumbbell</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>62.5</v>
+        <v>10</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2052,24 +2128,24 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Goblet Squat</t>
+          <t>Face Pull</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2082,24 +2158,24 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Half-Kneeling Single-Arm Overhead Press</t>
+          <t>Front Squat</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.18</v>
+        <v>0.7</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>barbell</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>10</v>
+        <v>62.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2112,16 +2188,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Hammer Curl</t>
+          <t>Goblet Squat</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2129,7 +2205,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7.5</v>
+        <v>20</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2142,7 +2218,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hanging Leg Raise</t>
+          <t>Half-Kneeling Single-Arm Overhead Press</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2151,15 +2227,15 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>0.18</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>bodyweight</t>
+          <t>dumbbell</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2172,24 +2248,24 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hip Thrusts</t>
+          <t>Hammer Curl</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.7</v>
+        <v>0.12</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>dumbbell</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>62.5</v>
+        <v>7.5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2202,7 +2278,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Incline Bench</t>
+          <t>Hanging Leg Raise</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2211,15 +2287,15 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.72</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>bodyweight</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2232,24 +2308,24 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Incline DB Bench</t>
+          <t>Hip Thrusts</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.28</v>
+        <v>0.7</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>barbell</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>62.5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2262,7 +2338,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Incline Dumbbell Curl</t>
+          <t>Incline Bench</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2271,15 +2347,15 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1</v>
+        <v>0.72</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>barbell</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>47.5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2292,24 +2368,24 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Kettlebell Swings</t>
+          <t>Incline DB Bench</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.2</v>
+        <v>0.28</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>kettlebell</t>
+          <t>dumbbell</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>16</v>
+        <v>17.5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2322,7 +2398,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Landmine Press</t>
+          <t>Incline Dumbbell Curl</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2331,15 +2407,15 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>dumbbell</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>7.5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2352,24 +2428,24 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lat Pulldown</t>
+          <t>Kettlebell Swings</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>kettlebell</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2382,7 +2458,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Lateral Raise</t>
+          <t>Landmine Press</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2391,15 +2467,15 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.09</v>
+        <v>0.35</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>barbell</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5</v>
+        <v>22.5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2412,24 +2488,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Leg Extension</t>
+          <t>Lat Pulldown</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2442,7 +2518,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Lying Dumbbell Curl</t>
+          <t>Lateral Raise</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2451,7 +2527,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -2472,24 +2548,24 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Neutral-Grip Pulldown</t>
+          <t>Leg Extension</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2502,7 +2578,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Overhead Carry</t>
+          <t>Lying Dumbbell Curl</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2511,7 +2587,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -2519,7 +2595,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2532,7 +2608,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Overhead Press</t>
+          <t>Neutral-Grip Pulldown</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2541,15 +2617,15 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>32.5</v>
+        <v>35</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -2562,7 +2638,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Overhead Tricep Extension</t>
+          <t>Overhead Carry</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2571,15 +2647,15 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>dumbbell</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2592,16 +2668,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RDLs</t>
+          <t>Overhead Press</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.65</v>
+        <v>0.58</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -2609,7 +2685,7 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>57.5</v>
+        <v>37.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2622,7 +2698,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rear Delt Fly</t>
+          <t>Overhead Tricep Extension</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2631,15 +2707,15 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.09</v>
+        <v>0.15</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2652,7 +2728,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Reverse Lunges</t>
+          <t>RDLs</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2661,15 +2737,15 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.2</v>
+        <v>0.65</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>barbell</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>17.5</v>
+        <v>57.5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2682,7 +2758,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Seated Cable Row</t>
+          <t>Rear Delt Fly</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2691,15 +2767,15 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.5</v>
+        <v>0.09</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>dumbbell</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2712,16 +2788,16 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Seated DB Press</t>
+          <t>Reverse Lunges</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2729,7 +2805,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>12.5</v>
+        <v>17.5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2742,7 +2818,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Shrugs</t>
+          <t>Seated Cable Row</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2751,15 +2827,15 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>17.5</v>
+        <v>35</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2772,7 +2848,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Single-Arm DB Bench Press</t>
+          <t>Seated DB Press</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2781,7 +2857,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2802,7 +2878,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Single-Arm DB Row</t>
+          <t>Shrugs</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2811,7 +2887,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.28</v>
+        <v>0.3</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2819,7 +2895,7 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -2832,7 +2908,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Single-Arm Lat Pulldown</t>
+          <t>Single-Arm DB Bench Press</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2841,15 +2917,15 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>dumbbell</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -2862,7 +2938,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Single-Arm Shrug</t>
+          <t>Single-Arm DB Row</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2871,7 +2947,7 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2879,7 +2955,7 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>10</v>
+        <v>17.5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -2892,24 +2968,24 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Single-Leg Leg Press</t>
+          <t>Single-Arm Lat Pulldown</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>machine</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -2922,16 +2998,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Single-Leg RDL</t>
+          <t>Single-Arm Shrug</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>0.15</v>
+        <v>0.18</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2952,7 +3028,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Single-Leg Squat (to Box)</t>
+          <t>Single-Leg Leg Press</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2961,15 +3037,15 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.16</v>
+        <v>0.6</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>machine</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2982,16 +3058,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Skull Crushers</t>
+          <t>Single-Leg RDL</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2999,7 +3075,7 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>10</v>
+        <v>12.5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -3012,24 +3088,24 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Speed Bench</t>
+          <t>Single-Leg Squat (to Box)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.55</v>
+        <v>0.16</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>dumbbell</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>32.5</v>
+        <v>15</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -3042,16 +3118,16 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Step Ups</t>
+          <t>Skull Crushers</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -3059,7 +3135,7 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>17.5</v>
+        <v>12.5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -3072,16 +3148,16 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Trap Bar Deadlift</t>
+          <t>Speed Bench</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.9</v>
+        <v>0.55</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -3089,7 +3165,7 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>80</v>
+        <v>37.5</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -3102,16 +3178,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Tricep Circuit (Dirty 30)</t>
+          <t>Step Ups</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -3119,7 +3195,7 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -3132,24 +3208,24 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tricep Pushdown</t>
+          <t>Trap Bar Deadlift</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>barbell</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -3162,16 +3238,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Walking Lunges</t>
+          <t>Tricep Circuit (Dirty 30)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -3179,7 +3255,7 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>17.5</v>
+        <v>7.5</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -3192,7 +3268,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Weighted Dead Bug</t>
+          <t>Tricep Pushdown</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -3201,15 +3277,15 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -3222,24 +3298,24 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Woodchop (Half Kneeling)</t>
+          <t>Walking Lunges</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>dumbbell</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5</v>
+        <v>17.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -3252,7 +3328,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Woodchop (Standing)</t>
+          <t>Weighted Dead Bug</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3261,15 +3337,15 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>dumbbell</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>7.5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -3282,7 +3358,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Z-Press</t>
+          <t>Woodchop (Half Kneeling)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3291,15 +3367,15 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>0.35</v>
+        <v>0.1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>cable</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -3308,6 +3384,66 @@
       </c>
       <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Woodchop (Standing)</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>cable</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>10</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Z-Press</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>barbell</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3320,7 +3456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -3376,184 +3512,124 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>Bicep Curl (Barbell)</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n">
+      <c r="B2" s="6" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="D2" s="4" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>barbell</t>
         </is>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>ratio floors out — computes 17.2kg, below the 20kg minimum, so the ratio never applies</t>
-        </is>
-      </c>
-      <c r="G2" s="4" t="inlineStr"/>
-      <c r="H2" s="4" t="inlineStr"/>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>ratio floors out — computes 19.8kg, below the 20kg minimum, so the ratio never applies</t>
+        </is>
+      </c>
+      <c r="G2" s="6" t="inlineStr"/>
+      <c r="H2" s="6" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Bottoms-Up KB Press</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="B3" s="6" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="n">
         <v>0.08</v>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>kettlebell</t>
         </is>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>ratio floors out — computes 4.6kg, below the 8kg minimum, so the ratio never applies</t>
-        </is>
-      </c>
-      <c r="G3" s="4" t="inlineStr"/>
-      <c r="H3" s="4" t="inlineStr"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>ratio floors out — computes 5.3kg, below the 8kg minimum, so the ratio never applies</t>
+        </is>
+      </c>
+      <c r="G3" s="6" t="inlineStr"/>
+      <c r="H3" s="6" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>Concentration Curl</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Explosive Landmine Press</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>barbell</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>ratio floors out — computes 16.5kg, below the 20kg minimum, so the ratio never applies</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr"/>
+      <c r="H4" s="6" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Incline Y Raise</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
         <is>
           <t>dumbbell</t>
         </is>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E5" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <t>ratio floors out — computes 4.6kg, below the 5kg minimum, so the ratio never applies</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr"/>
-      <c r="H4" s="4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Dumbbell Kickback</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>dumbbell</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>ratio floors out — computes 4.6kg, below the 5kg minimum, so the ratio never applies</t>
-        </is>
-      </c>
-      <c r="G5" s="4" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>Explosive Landmine Press</t>
-        </is>
-      </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>barbell</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>ratio floors out — computes 14.3kg, below the 20kg minimum, so the ratio never applies</t>
-        </is>
-      </c>
-      <c r="G6" s="4" t="inlineStr"/>
-      <c r="H6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Incline Y Raise</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>dumbbell</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>ratio floors out — computes 4.0kg, below the 5kg minimum, so the ratio never applies</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
+      <c r="G5" s="6" t="inlineStr"/>
+      <c r="H5" s="6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3622,184 +3698,184 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>Back Extension</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>squat</t>
         </is>
       </c>
-      <c r="C2" s="6" t="n">
+      <c r="C2" s="4" t="n">
         <v>0.15</v>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>dumbbell</t>
         </is>
       </c>
-      <c r="E2" s="6" t="n">
+      <c r="E2" s="4" t="n">
         <v>12.5</v>
       </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G2" s="6" t="inlineStr"/>
-      <c r="H2" s="6" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr"/>
+      <c r="H2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>Hamstring Curl</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>squat</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>machine</t>
         </is>
       </c>
-      <c r="E3" s="6" t="n">
+      <c r="E3" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="6" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr"/>
+      <c r="H3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>High Box Squat</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>squat</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="4" t="n">
         <v>0.9</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>barbell</t>
         </is>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E4" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>Single-Arm DB Floor Press</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="n">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>0.22</v>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>dumbbell</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="inlineStr"/>
+      <c r="E5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>Single-Leg Hip Thrust</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>squat</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>dumbbell</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E6" s="4" t="n">
         <v>17.5</v>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr"/>
+      <c r="H6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>Speed Trap Bar Deadlift</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>squat</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>barbell</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E7" s="4" t="n">
         <v>40</v>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/LOAD_RATIO_REVIEW_2026-07-28.xlsx
+++ b/docs/LOAD_RATIO_REVIEW_2026-07-28.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A38"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="82" customWidth="1" min="1" max="1"/>
@@ -653,26 +653,33 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>STILL UNRULED: the minimums for cable (5), machine (10) and dumbbell (5) are</t>
+          <t>EVERY EQUIPMENT KIND IS RULED. Minimums and lattices both carry a Sam</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>inherited, not ruled. Note the dumbbell tension — the ruled lattice starts at</t>
+          <t>ruling and live in one owner (src/data/equipmentLattice.ts). The dumbbell</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1 kg but the inherited minimum is 5 kg, so 1-4 kg dumbbells are loadable and</t>
+          <t>minimum of 1 kg matches its lattice start — before Sam ruled it the minimum</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
+        <is>
+          <t>was 5 kg while the ladder began at 1, so 1-4 kg dumbbells were loadable and</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>never prescribed.</t>
         </is>
@@ -1032,11 +1039,11 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>NO — inherited</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1061,7 +1068,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>NO — inherited</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1105,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>1–10 kg by 1, then 2.5 kg steps</t>
+          <t>1-10 kg by 1, then 2.5 kg steps</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1107,11 +1114,11 @@
         </is>
       </c>
       <c r="D6" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>NO — inherited</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2743,7 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>

--- a/docs/LOAD_RATIO_REVIEW_2026-07-28.xlsx
+++ b/docs/LOAD_RATIO_REVIEW_2026-07-28.xlsx
@@ -2385,7 +2385,7 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>barbell</t>
         </is>
       </c>
     </row>

--- a/docs/LOAD_RATIO_REVIEW_2026-07-28.xlsx
+++ b/docs/LOAD_RATIO_REVIEW_2026-07-28.xlsx
@@ -458,9 +458,7 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-    </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
@@ -482,9 +480,7 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
@@ -513,9 +509,7 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-    </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
@@ -537,9 +531,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -568,9 +560,7 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-    </row>
+    <row r="21"/>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
@@ -585,9 +575,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
@@ -602,9 +590,7 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" t="inlineStr"/>
-    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
@@ -647,9 +633,7 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr"/>
-    </row>
+    <row r="34"/>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
@@ -1158,7 +1142,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D73"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1232,7 +1216,7 @@
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Barbell Row</t>
+          <t>Bent Row</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -2350,20 +2334,20 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>Single-Leg Squat (to Box)</t>
-        </is>
-      </c>
-      <c r="B60" s="4" t="inlineStr">
-        <is>
-          <t>squat</t>
-        </is>
-      </c>
-      <c r="C60" s="4" t="n">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>B-Stance RDL</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>squat</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
         <v>0.15</v>
       </c>
-      <c r="D60" s="4" t="inlineStr">
+      <c r="D60" t="inlineStr">
         <is>
           <t>dumbbell</t>
         </is>
@@ -2372,27 +2356,27 @@
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>Skull Crushers</t>
+          <t>Single-Leg Squat (to Box)</t>
         </is>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0.2</v>
+        <v>0.15</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>dumbbell</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
         <is>
-          <t>Speed Bench</t>
+          <t>Skull Crushers</t>
         </is>
       </c>
       <c r="B62" s="4" t="inlineStr">
@@ -2401,7 +2385,7 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>0.55</v>
+        <v>0.2</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
@@ -2412,16 +2396,16 @@
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
         <is>
-          <t>Speed Trap Bar Deadlift</t>
+          <t>Speed Bench</t>
         </is>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
@@ -2432,7 +2416,7 @@
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
         <is>
-          <t>Step Ups</t>
+          <t>Speed Trap Bar Deadlift</t>
         </is>
       </c>
       <c r="B64" s="4" t="inlineStr">
@@ -2441,27 +2425,27 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.2</v>
+        <v>0.45</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>barbell</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
         <is>
-          <t>Suitcase Carry</t>
+          <t>Step Ups</t>
         </is>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
@@ -2472,47 +2456,47 @@
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
         <is>
-          <t>Trap Bar Deadlift</t>
+          <t>Suitcase Carry</t>
         </is>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>barbell</t>
+          <t>dumbbell</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="inlineStr">
         <is>
-          <t>Tricep Circuit (Dirty 30)</t>
+          <t>Trap Bar Deadlift</t>
         </is>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>barbell</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="4" t="inlineStr">
         <is>
-          <t>Tricep Pushdown</t>
+          <t>Tricep Circuit (Dirty 30)</t>
         </is>
       </c>
       <c r="B68" s="4" t="inlineStr">
@@ -2521,23 +2505,23 @@
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>dumbbell</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="4" t="inlineStr">
         <is>
-          <t>Walking Lunges</t>
+          <t>Tricep Pushdown</t>
         </is>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>squat</t>
+          <t>bench</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
@@ -2545,23 +2529,23 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>dumbbell</t>
+          <t>cable</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
         <is>
-          <t>Weighted Dead Bug</t>
+          <t>Walking Lunges</t>
         </is>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>bench</t>
+          <t>squat</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
@@ -2572,7 +2556,7 @@
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
         <is>
-          <t>Woodchop (Half Kneeling)</t>
+          <t>Weighted Dead Bug</t>
         </is>
       </c>
       <c r="B71" s="4" t="inlineStr">
@@ -2585,14 +2569,14 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>cable</t>
+          <t>dumbbell</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="4" t="inlineStr">
         <is>
-          <t>Woodchop (Standing)</t>
+          <t>Woodchop (Half Kneeling)</t>
         </is>
       </c>
       <c r="B72" s="4" t="inlineStr">
@@ -2601,7 +2585,7 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>0.15</v>
+        <v>0.1</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
@@ -2612,18 +2596,38 @@
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
         <is>
+          <t>Woodchop (Standing)</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>cable</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
           <t>Z-Press</t>
         </is>
       </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>bench</t>
-        </is>
-      </c>
-      <c r="C73" s="4" t="n">
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>bench</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="D73" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>barbell</t>
         </is>
